--- a/public/docs/inventario.xlsx
+++ b/public/docs/inventario.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danielrodriguez/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\isare\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6083461-B8AD-0549-869F-1338A88D02F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77950BB1-9223-45CF-8D7D-549732FFC3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" xr2:uid="{0CF9EDC5-61BD-408E-854A-B04924EDC026}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0CF9EDC5-61BD-408E-854A-B04924EDC026}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="91">
   <si>
     <t>EAN</t>
   </si>
@@ -44,27 +33,6 @@
     <t xml:space="preserve">NOMBRE </t>
   </si>
   <si>
-    <t xml:space="preserve">SUSNTACIA </t>
-  </si>
-  <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t>S2</t>
-  </si>
-  <si>
-    <t>S3</t>
-  </si>
-  <si>
-    <t>S4</t>
-  </si>
-  <si>
-    <t>CADUCIDAD</t>
-  </si>
-  <si>
-    <t>LOTE</t>
-  </si>
-  <si>
     <t>7501493980396</t>
   </si>
   <si>
@@ -74,9 +42,6 @@
     <t>AMFOTERICINA B  SOL 50MG INY C/1 FCO AMP</t>
   </si>
   <si>
-    <t>AB00525</t>
-  </si>
-  <si>
     <t>7501493802315</t>
   </si>
   <si>
@@ -86,105 +51,60 @@
     <t>CEFTRIAXONA IV  1G/10ML C/FCO AMP</t>
   </si>
   <si>
-    <t>CX03324</t>
-  </si>
-  <si>
     <t>CEFTRIAXONA IV 1G/10ML C/FCO AMP</t>
   </si>
   <si>
-    <t>CX00225</t>
-  </si>
-  <si>
-    <t>CX01725</t>
-  </si>
-  <si>
     <t>ALFANAR® SOL 50MG INY C/1 FCO AMP</t>
   </si>
   <si>
     <t>CASPOFUNGINA  SOL 50MG INY C/1 FCO AMP</t>
   </si>
   <si>
-    <t>CAS00125</t>
-  </si>
-  <si>
     <t>SULOVAL® 1G SOL INY C/1 FCO AMP</t>
   </si>
   <si>
     <t>CEFEPIMA  1G SOL INY C/1 FCO AMP</t>
   </si>
   <si>
-    <t>CEE1925</t>
-  </si>
-  <si>
     <t xml:space="preserve">SOLUVAL 500 MG SOL INY </t>
   </si>
   <si>
     <t xml:space="preserve">CEFEPIMA 500MG SOL INY C/1 FC AMP </t>
   </si>
   <si>
-    <t>CE00625</t>
-  </si>
-  <si>
     <t>7501493874718</t>
   </si>
   <si>
     <t>CORBUSIN SOL 250MG/20ML INY C/1 FCO AMP</t>
   </si>
   <si>
-    <t>DB00324</t>
-  </si>
-  <si>
-    <t>DB00124</t>
-  </si>
-  <si>
     <t>DANMIDRAT® 200MCG/2ML C/1 FCOS AMP 2ML</t>
   </si>
   <si>
     <t>DEXMEDETOMIDINA   200MCG/2ML C/1 FCOS AMP 2ML</t>
   </si>
   <si>
-    <t>XM00425</t>
-  </si>
-  <si>
     <t>DANMIDRAT® 200MCG/2ML C/5 FCOS AMP 2ML</t>
   </si>
   <si>
-    <t>XM00225</t>
-  </si>
-  <si>
-    <t>XM00525</t>
-  </si>
-  <si>
     <t xml:space="preserve">DIFENHISTAT 10MG/1ML FC 10ML </t>
   </si>
   <si>
     <t xml:space="preserve">DIFENHIDRAMINA 10MG/1ML FC 10ML </t>
   </si>
   <si>
-    <t>DH02325</t>
-  </si>
-  <si>
-    <t>DH03725</t>
-  </si>
-  <si>
     <t>DONECOL® SOL 500MG INY C/1 FCO AMP</t>
   </si>
   <si>
     <t>DEXRAZOXANO DONECOL® SOL 500MG INY C/1 FCO AMP</t>
   </si>
   <si>
-    <t>EX00524</t>
-  </si>
-  <si>
     <t>DROMETAK 30MG/ML C3 AMP</t>
   </si>
   <si>
     <t>KETOROLACO  30MG/ML C3 AMP</t>
   </si>
   <si>
-    <t>KEI00125</t>
-  </si>
-  <si>
     <t>7501493802438</t>
   </si>
   <si>
@@ -194,21 +114,6 @@
     <t>ETAMSILATO CAPHEMASIL® SOL 250MG/2ML INY C/4 AMP</t>
   </si>
   <si>
-    <t>TA00425</t>
-  </si>
-  <si>
-    <t>TA00525</t>
-  </si>
-  <si>
-    <t>TA00725</t>
-  </si>
-  <si>
-    <t>TA00825</t>
-  </si>
-  <si>
-    <t>TA00925</t>
-  </si>
-  <si>
     <t>7501493868915</t>
   </si>
   <si>
@@ -218,54 +123,24 @@
     <t>FENITOINA SÓDICA COMVUFEN® SOL 250MG/5ML INY C/1 AMP</t>
   </si>
   <si>
-    <t>FS00325</t>
-  </si>
-  <si>
-    <t>FS01125</t>
-  </si>
-  <si>
-    <t>FS01025</t>
-  </si>
-  <si>
     <t xml:space="preserve">FINATAK  1G SOL INY F.A. </t>
   </si>
   <si>
     <t xml:space="preserve">ERTAPENEM 1G SOL INY F.A. </t>
   </si>
   <si>
-    <t>ET00325</t>
-  </si>
-  <si>
-    <t>ET01925</t>
-  </si>
-  <si>
-    <t>ET03025</t>
-  </si>
-  <si>
-    <t>ET03625</t>
-  </si>
-  <si>
     <t>VIRAPREX® SOL 500MG INY C/1 FCO AMP</t>
   </si>
   <si>
     <t>GANCICLOVIR SOL 500MG INY C/1 FCO AMP</t>
   </si>
   <si>
-    <t>GA00125</t>
-  </si>
-  <si>
-    <t>GA00225</t>
-  </si>
-  <si>
     <t xml:space="preserve">TRALIKEM IM 100MG C/6 AMP </t>
   </si>
   <si>
     <t xml:space="preserve">KETOPROFENO 100MG C/6 AMP IM </t>
   </si>
   <si>
-    <t>KF00225</t>
-  </si>
-  <si>
     <t>7501493873308</t>
   </si>
   <si>
@@ -275,12 +150,6 @@
     <t>KETOPROFENO SOL 100MG INY C/3 FCO AMP</t>
   </si>
   <si>
-    <t>KR00825</t>
-  </si>
-  <si>
-    <t>KR01125</t>
-  </si>
-  <si>
     <t>7501493802551</t>
   </si>
   <si>
@@ -290,12 +159,6 @@
     <t>PARECOXIB 40MG SOL INY C/2 FCOS AMP</t>
   </si>
   <si>
-    <t>PA02225</t>
-  </si>
-  <si>
-    <t>PA00126</t>
-  </si>
-  <si>
     <t>7501493802513</t>
   </si>
   <si>
@@ -305,9 +168,6 @@
     <t xml:space="preserve">LEVETIRACETAM 100MG/1ML C/10 FCOS AMP </t>
   </si>
   <si>
-    <t>LEV00126</t>
-  </si>
-  <si>
     <t>7501493867895</t>
   </si>
   <si>
@@ -317,21 +177,12 @@
     <t>MEROPENEM SOL 500MG INY C/FCO AMP</t>
   </si>
   <si>
-    <t>ME00525</t>
-  </si>
-  <si>
     <t xml:space="preserve">MERMAVIE® SOL 1G INY C/1 FCO AMP </t>
   </si>
   <si>
     <t xml:space="preserve">MEROPENEM  SOL 1G INY C/1 FCO AMP </t>
   </si>
   <si>
-    <t>MR00326</t>
-  </si>
-  <si>
-    <t>MR02025</t>
-  </si>
-  <si>
     <t>7501493801493</t>
   </si>
   <si>
@@ -341,9 +192,6 @@
     <t>MILRINONA SOL 1MG/1ML INY C/3 AMP</t>
   </si>
   <si>
-    <t>ML00124</t>
-  </si>
-  <si>
     <t>7501493888944</t>
   </si>
   <si>
@@ -353,33 +201,18 @@
     <t>METOPROLOL 100MG C/20 TAB</t>
   </si>
   <si>
-    <t>M00624</t>
-  </si>
-  <si>
     <t xml:space="preserve">METISONA 500MG/8ML SOL INY C/1 FCO AMP </t>
   </si>
   <si>
     <t xml:space="preserve">METILPREDNISOLONA 500MG/8ML SOL INY C/1 FCO AMP </t>
   </si>
   <si>
-    <t>MP00525</t>
-  </si>
-  <si>
-    <t>MP00725</t>
-  </si>
-  <si>
     <t xml:space="preserve">METISONA SOL 500MG/8ML INY C/50 FCOS AMP </t>
   </si>
   <si>
     <t xml:space="preserve">METILPREDNISOLONA  SOL 500MG/8ML INY C/50 FCOS AMP </t>
   </si>
   <si>
-    <t>MP01525</t>
-  </si>
-  <si>
-    <t>MP01625</t>
-  </si>
-  <si>
     <t>7501493874640</t>
   </si>
   <si>
@@ -389,15 +222,6 @@
     <t>NIMODIPINO SOL 10MG/50ML INY C/1 FCO AMP</t>
   </si>
   <si>
-    <t>NPI00725</t>
-  </si>
-  <si>
-    <t>NPI02725</t>
-  </si>
-  <si>
-    <t>NPI02525</t>
-  </si>
-  <si>
     <t>7501493874633</t>
   </si>
   <si>
@@ -407,21 +231,12 @@
     <t>NOREPINEFRINA  SOL 4MG/4ML INY C/50 AMP</t>
   </si>
   <si>
-    <t>N00324</t>
-  </si>
-  <si>
-    <t>N00525</t>
-  </si>
-  <si>
     <t xml:space="preserve">SOFTAMICID SOL 4MG/4ML INY C/10 AMP </t>
   </si>
   <si>
     <t>NOREPINEFRINA  SOL 4MG/4ML INY C/10 AMP</t>
   </si>
   <si>
-    <t>N00425</t>
-  </si>
-  <si>
     <t>7501493980433</t>
   </si>
   <si>
@@ -431,15 +246,6 @@
     <t>OMEPRAZOL SOL 40MG/10ML INY C/1 FCO AMP</t>
   </si>
   <si>
-    <t>OI01725</t>
-  </si>
-  <si>
-    <t>OI02025</t>
-  </si>
-  <si>
-    <t>OI02325</t>
-  </si>
-  <si>
     <t>7501493873872</t>
   </si>
   <si>
@@ -449,54 +255,36 @@
     <t>PARACETAMOL SOL 1G/100ML INY C/1 FCO AMP</t>
   </si>
   <si>
-    <t>PO18425</t>
-  </si>
-  <si>
     <t xml:space="preserve">VERAKEN® SOL 5MG/2ML INY C/1 AMP </t>
   </si>
   <si>
     <t xml:space="preserve">VERAPAMILO VERAKEN® SOL 5MG/2ML INY C/1 AMP </t>
   </si>
   <si>
-    <t>VP00225</t>
-  </si>
-  <si>
     <t>VARAMYN 500MG SOL INY FC C/1</t>
   </si>
   <si>
     <t xml:space="preserve">VANCOMICINA 500MG SOL INY C/1 FC </t>
   </si>
   <si>
-    <t>VA00425</t>
-  </si>
-  <si>
     <t>VARAMYN 1G SOL INY FC C/1</t>
   </si>
   <si>
     <t xml:space="preserve">VANCOMICINA 1G SOL INY C/1 FC </t>
   </si>
   <si>
-    <t>VN00325</t>
-  </si>
-  <si>
     <t xml:space="preserve">ANDUREST 2MG/ML C/5 AMP 20 ML </t>
   </si>
   <si>
     <t xml:space="preserve">ROPIVACAINA 2MG/ML C/5 AMP 20ML </t>
   </si>
   <si>
-    <t>RA00225</t>
-  </si>
-  <si>
     <t xml:space="preserve">ANDUREST 7.5MG /ML C/5 AMP 20ML </t>
   </si>
   <si>
     <t xml:space="preserve">ROPIVACAINA 7.5MG /ML C/5 AMP 20ML </t>
   </si>
   <si>
-    <t>RN00325</t>
-  </si>
-  <si>
     <t>RED</t>
   </si>
   <si>
@@ -504,15 +292,18 @@
   </si>
   <si>
     <t xml:space="preserve">SECO </t>
+  </si>
+  <si>
+    <t>SUSTANCIA</t>
+  </si>
+  <si>
+    <t>EXISTENCIA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -563,7 +354,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -574,9 +365,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -584,183 +372,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <font>
         <strike val="0"/>
@@ -985,22 +597,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7E8065B8-D1CE-411A-8191-CCAF2C190626}" name="Tabla3" displayName="Tabla3" ref="A1:J61" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J61" xr:uid="{7E8065B8-D1CE-411A-8191-CCAF2C190626}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7E8065B8-D1CE-411A-8191-CCAF2C190626}" name="Tabla3" displayName="Tabla3" ref="A1:E61" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:E61" xr:uid="{7E8065B8-D1CE-411A-8191-CCAF2C190626}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E61">
     <sortCondition ref="B2:B61"/>
   </sortState>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{83D05D03-881D-42F5-8075-FBAF9A1563D8}" name="EAN" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{01265CF5-941A-4718-BF35-B7502685EBB5}" name="NOMBRE " dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{4EEF6230-9AC1-402E-9156-C99715E20B69}" name="SUSNTACIA " dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{51A04CDD-9A2B-F849-A018-6DC105F2FD96}" name="RED" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{7EC3B451-394C-489F-9D39-BF0AFC73526A}" name="S1" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{30E2C9A4-8BCC-46C5-90D3-A5153B4D6CDB}" name="S2" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{464AABE4-C314-4C67-950A-8CDE16C1FA7C}" name="S3" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{5D391F0A-BD58-42E7-8095-6D72DE702766}" name="S4" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{CD97BCB7-B8DE-4B4D-A06B-7DA54657F5D8}" name="CADUCIDAD" dataDxfId="0"/>
-    <tableColumn id="8" xr3:uid="{BFB2CE8B-0930-40B5-BCC8-B0E84228C11D}" name="LOTE" dataDxfId="1"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{83D05D03-881D-42F5-8075-FBAF9A1563D8}" name="EAN" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{01265CF5-941A-4718-BF35-B7502685EBB5}" name="NOMBRE " dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{4EEF6230-9AC1-402E-9156-C99715E20B69}" name="SUSTANCIA" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{51A04CDD-9A2B-F849-A018-6DC105F2FD96}" name="RED" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{7EC3B451-394C-489F-9D39-BF0AFC73526A}" name="EXISTENCIA" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1323,18 +930,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA7CDD2C-2AFA-4E05-8AAF-FF4E46CB157F}">
-  <dimension ref="A1:J61"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E61"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.1640625" customWidth="1"/>
-    <col min="2" max="2" width="66.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.109375" customWidth="1"/>
+    <col min="2" max="2" width="66.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="86.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.1640625" style="5" customWidth="1"/>
-    <col min="9" max="9" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.109375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="20.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1342,1588 +948,1033 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>89</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>153</v>
+        <v>86</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>7501493874701</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>154</v>
+        <v>87</v>
       </c>
       <c r="E2" s="1">
         <v>28</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="4">
-        <v>46523</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>7501493803169</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E3" s="1">
         <v>3</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="4">
-        <v>46692</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>7501493803190</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>151</v>
+        <v>85</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E4" s="1">
         <v>35</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="4">
-        <v>46692</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>116</v>
+        <v>64</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E5" s="1">
         <v>30</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="4">
-        <v>46722</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>116</v>
+        <v>64</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E6" s="1">
         <v>20</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="4">
-        <v>46675</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>116</v>
+        <v>64</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="4">
-        <v>46675</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="4">
-        <v>46174</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>154</v>
+        <v>87</v>
       </c>
       <c r="E9" s="1">
         <v>20</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="4">
-        <v>46569</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E10" s="1">
         <v>18</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="4">
-        <v>46522</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E11" s="1">
         <v>41</v>
       </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="4">
-        <v>46553</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E12" s="1">
         <v>51</v>
       </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="4">
-        <v>46631</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
       </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="4">
-        <v>46661</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
       </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="4">
-        <v>46706</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
       </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="4">
-        <v>46492</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E16" s="1">
         <v>18</v>
       </c>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="4">
-        <v>46736</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E17" s="1">
         <v>32</v>
       </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="4">
-        <v>46706</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E18" s="1">
         <v>40</v>
       </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="4">
-        <v>46357</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E19" s="1">
         <v>18</v>
       </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="4">
-        <v>46204</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>7501493803145</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E20" s="1">
         <v>49</v>
       </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="4">
-        <v>46569</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>7501493803145</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
       </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="4">
-        <v>46569</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>7501493803145</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E22" s="1">
         <v>68</v>
       </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="4">
-        <v>46661</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>7501493874695</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E23" s="1">
         <v>18</v>
       </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="4">
-        <v>46583</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>7501493874695</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E24" s="1">
         <v>10</v>
       </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="4">
-        <v>46661</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>7501493802483</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E25" s="1">
         <v>6</v>
       </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="4">
-        <v>46341</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>7501493980495</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E26" s="1">
         <v>467</v>
       </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="4">
-        <v>46631</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>7501493802254</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E27" s="1">
         <v>14</v>
       </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="4">
-        <v>46388</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>7501493802254</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E28" s="1">
         <v>30</v>
       </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="4">
-        <v>46419</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>7501493802254</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E29" s="1">
         <v>20</v>
       </c>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="4">
-        <v>46492</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>7501493802254</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E30" s="1">
         <v>30</v>
       </c>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="4">
-        <v>46508</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E31" s="1">
         <v>10</v>
       </c>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="4">
-        <v>46692</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E32" s="1">
         <v>20</v>
       </c>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="4">
-        <v>46784</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E33" s="1">
         <v>17</v>
       </c>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="4">
-        <v>46784</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
       </c>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="4">
-        <v>46235</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E35" s="1">
         <v>928</v>
       </c>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="4">
-        <v>46631</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>7501493867901</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E36" s="1">
         <v>150</v>
       </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="4">
-        <v>46631</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>7501493867901</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E37" s="1">
         <v>44</v>
       </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="4">
-        <v>46447</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E38" s="1">
         <v>7</v>
       </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="4">
-        <v>46522</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>7501493980242</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E39" s="1">
         <v>7</v>
       </c>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="4">
-        <v>46553</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>7501493980242</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E40" s="1">
         <v>48</v>
       </c>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="4">
-        <v>46583</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>7501493867734</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
       </c>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="4">
-        <v>46692</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>7501493867734</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E42" s="1">
         <v>10</v>
       </c>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="4">
-        <v>46722</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E43" s="1">
         <v>40</v>
       </c>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="4">
-        <v>46645</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E44" s="1">
         <v>300</v>
       </c>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="4">
-        <v>46675</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E45" s="1">
         <v>70</v>
       </c>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="4">
-        <v>46692</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>7501493869738</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>126</v>
+        <v>69</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E46" s="1">
         <v>4</v>
       </c>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="4">
-        <v>46553</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>121</v>
+        <v>66</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
       </c>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="4">
-        <v>46296</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>121</v>
+        <v>66</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E48" s="1">
         <v>27</v>
       </c>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="4">
-        <v>46583</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>7501493873230</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E49" s="1">
         <v>30</v>
       </c>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="4">
-        <v>46553</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>7501493873216</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E50" s="1">
         <v>240</v>
       </c>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="4">
-        <v>46692</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>7501493873261</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E51" s="1">
         <v>5</v>
       </c>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="4">
-        <v>46569</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E52" s="1">
         <v>4</v>
       </c>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="4">
-        <v>46447</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E53" s="1">
         <v>40</v>
       </c>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="4">
-        <v>46492</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>7501493803121</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>145</v>
+        <v>81</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E54" s="1">
         <v>64</v>
       </c>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="4">
-        <v>46645</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>7501493803114</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E55" s="1">
         <v>340</v>
       </c>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="4">
-        <v>46645</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>7501493871540</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E56" s="1">
         <v>28</v>
       </c>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="4">
-        <v>46569</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>7501493874688</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E57" s="1">
         <v>14</v>
       </c>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="4">
-        <v>46419</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>7501493874688</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E58" s="1">
         <v>10</v>
       </c>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="4">
-        <v>46433</v>
-      </c>
-      <c r="J58" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E59" s="1">
         <v>100</v>
       </c>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="4">
-        <v>46539</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E60" s="1">
         <v>50</v>
       </c>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="4">
-        <v>46188</v>
-      </c>
-      <c r="J60" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="E61" s="1">
         <v>94</v>
-      </c>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="4">
-        <v>46266</v>
-      </c>
-      <c r="J61" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/public/docs/inventario.xlsx
+++ b/public/docs/inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\isare\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77950BB1-9223-45CF-8D7D-549732FFC3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF2D5C6-B9F0-4B16-B786-EF812D23264E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0CF9EDC5-61BD-408E-854A-B04924EDC026}"/>
   </bookViews>
@@ -354,19 +354,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -386,8 +383,38 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -400,12 +427,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -425,8 +446,8 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -439,12 +460,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -460,8 +475,8 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -474,12 +489,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -495,8 +504,8 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -509,12 +518,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -531,8 +534,8 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -545,43 +548,7 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -597,17 +564,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7E8065B8-D1CE-411A-8191-CCAF2C190626}" name="Tabla3" displayName="Tabla3" ref="A1:E61" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7E8065B8-D1CE-411A-8191-CCAF2C190626}" name="Tabla3" displayName="Tabla3" ref="A1:E61" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
   <autoFilter ref="A1:E61" xr:uid="{7E8065B8-D1CE-411A-8191-CCAF2C190626}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E61">
     <sortCondition ref="B2:B61"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{83D05D03-881D-42F5-8075-FBAF9A1563D8}" name="EAN" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{01265CF5-941A-4718-BF35-B7502685EBB5}" name="NOMBRE " dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{4EEF6230-9AC1-402E-9156-C99715E20B69}" name="SUSTANCIA" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{51A04CDD-9A2B-F849-A018-6DC105F2FD96}" name="RED" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{7EC3B451-394C-489F-9D39-BF0AFC73526A}" name="EXISTENCIA" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{83D05D03-881D-42F5-8075-FBAF9A1563D8}" name="EAN" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{01265CF5-941A-4718-BF35-B7502685EBB5}" name="NOMBRE " dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{4EEF6230-9AC1-402E-9156-C99715E20B69}" name="SUSTANCIA" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{51A04CDD-9A2B-F849-A018-6DC105F2FD96}" name="RED" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{7EC3B451-394C-489F-9D39-BF0AFC73526A}" name="EXISTENCIA" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -936,1044 +903,1044 @@
     <col min="1" max="1" width="28.109375" customWidth="1"/>
     <col min="2" max="2" width="66.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="86.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="32.109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>7501493874701</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>7501493803169</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="D3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>7501493803190</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="D4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" s="2">
         <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" s="1">
+      <c r="D5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="2">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" s="1">
+      <c r="D6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="D7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" s="1">
+      <c r="D8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E10" s="1">
+      <c r="D10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="2">
         <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" s="1">
+      <c r="D11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" s="2">
         <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" s="1">
+      <c r="D12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="2">
         <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" s="1">
+      <c r="D13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="2">
         <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E14" s="1">
+      <c r="D14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="2">
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E15" s="1">
+      <c r="D15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E16" s="1">
+      <c r="D16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E16" s="2">
         <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E17" s="1">
+      <c r="D17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E17" s="2">
         <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E18" s="1">
+      <c r="D18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E19" s="1">
+      <c r="D19" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" s="2">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
+      <c r="A20" s="3">
         <v>7501493803145</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20" s="1">
+      <c r="D20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E20" s="2">
         <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
+      <c r="A21" s="3">
         <v>7501493803145</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E21" s="1">
+      <c r="D21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
+      <c r="A22" s="3">
         <v>7501493803145</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E22" s="1">
+      <c r="D22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="2">
         <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
+      <c r="A23" s="3">
         <v>7501493874695</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E23" s="1">
+      <c r="D23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E23" s="2">
         <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
+      <c r="A24" s="3">
         <v>7501493874695</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E24" s="1">
+      <c r="D24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" s="2">
         <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
+      <c r="A25" s="3">
         <v>7501493802483</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E25" s="1">
+      <c r="D25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
+      <c r="A26" s="3">
         <v>7501493980495</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E26" s="1">
+      <c r="D26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E26" s="2">
         <v>467</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
+      <c r="A27" s="3">
         <v>7501493802254</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E27" s="1">
+      <c r="D27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
+      <c r="A28" s="3">
         <v>7501493802254</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E28" s="1">
+      <c r="D28" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E28" s="2">
         <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
+      <c r="A29" s="3">
         <v>7501493802254</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E29" s="1">
+      <c r="D29" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E29" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
+      <c r="A30" s="3">
         <v>7501493802254</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E30" s="1">
+      <c r="D30" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E30" s="2">
         <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E31" s="1">
+      <c r="D31" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" s="2">
         <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E32" s="1">
+      <c r="D32" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E32" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E33" s="1">
+      <c r="D33" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E33" s="2">
         <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E34" s="1">
+      <c r="D34" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E34" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E35" s="1">
+      <c r="D35" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E35" s="2">
         <v>928</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
+      <c r="A36" s="3">
         <v>7501493867901</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E36" s="1">
+      <c r="D36" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E36" s="2">
         <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
+      <c r="A37" s="3">
         <v>7501493867901</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E37" s="1">
+      <c r="D37" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E37" s="2">
         <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E38" s="1">
+      <c r="D38" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E38" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A39" s="2">
+      <c r="A39" s="3">
         <v>7501493980242</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E39" s="1">
+      <c r="D39" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E39" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A40" s="2">
+      <c r="A40" s="3">
         <v>7501493980242</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E40" s="1">
+      <c r="D40" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E40" s="2">
         <v>48</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A41" s="2">
+      <c r="A41" s="3">
         <v>7501493867734</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E41" s="1">
+      <c r="D41" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E41" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
+      <c r="A42" s="3">
         <v>7501493867734</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E42" s="1">
+      <c r="D42" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E42" s="2">
         <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E43" s="1">
+      <c r="D43" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E43" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E44" s="1">
+      <c r="D44" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E44" s="2">
         <v>300</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E45" s="1">
+      <c r="D45" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E45" s="2">
         <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A46" s="2">
+      <c r="A46" s="3">
         <v>7501493869738</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E46" s="1">
+      <c r="D46" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E46" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E47" s="1">
+      <c r="D47" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E47" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E48" s="1">
+      <c r="D48" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E48" s="2">
         <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A49" s="2">
+      <c r="A49" s="3">
         <v>7501493873230</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E49" s="1">
+      <c r="D49" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E49" s="2">
         <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A50" s="2">
+      <c r="A50" s="3">
         <v>7501493873216</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E50" s="1">
+      <c r="D50" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E50" s="2">
         <v>240</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A51" s="2">
+      <c r="A51" s="3">
         <v>7501493873261</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E51" s="1">
+      <c r="D51" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E51" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E52" s="1">
+      <c r="D52" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E52" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E53" s="1">
+      <c r="D53" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E53" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A54" s="2">
+      <c r="A54" s="3">
         <v>7501493803121</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E54" s="1">
+      <c r="D54" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E54" s="2">
         <v>64</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A55" s="2">
+      <c r="A55" s="3">
         <v>7501493803114</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E55" s="1">
+      <c r="D55" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E55" s="2">
         <v>340</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A56" s="2">
+      <c r="A56" s="3">
         <v>7501493871540</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E56" s="1">
+      <c r="D56" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E56" s="2">
         <v>28</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A57" s="2">
+      <c r="A57" s="3">
         <v>7501493874688</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E57" s="1">
+      <c r="D57" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E57" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A58" s="2">
+      <c r="A58" s="3">
         <v>7501493874688</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E58" s="1">
+      <c r="D58" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E58" s="2">
         <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D59" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E59" s="1">
+      <c r="D59" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E59" s="2">
         <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D60" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E60" s="1">
+      <c r="D60" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E60" s="2">
         <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
+      <c r="A61" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C61" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E61" s="1">
+      <c r="D61" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E61" s="2">
         <v>94</v>
       </c>
     </row>
